--- a/astro-site/public/dl/pastry-shop-checklist-templates/BONUS-02-pastry-shop-holiday-calendar.xlsx
+++ b/astro-site/public/dl/pastry-shop-checklist-templates/BONUS-02-pastry-shop-holiday-calendar.xlsx
@@ -583,7 +583,7 @@
     <row r="7">
       <c r="B7" s="19" t="inlineStr">
         <is>
-          <t>▸ Add your local dates (fairs, festivals). UK note: add Mothering Sunday (March), bank holidays and Boxing Day in the free rows</t>
+          <t>▸ Add your local dates (fairs, festivals). UK note: add Mothering Sunday (3 weeks before Easter: March or early April), bank holidays and Boxing Day in the free rows</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>Rosca de Reyes (Three Kings bread) for January 6 and King cake until Mardi Gras (cream, cream cheese or praline filling)</t>
+          <t>Rosca de Reyes (Three Kings bread) for January 6, King cake until Mardi Gras (cream, cream cheese or praline filling) and paczki for Fat Tuesday</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>May–Jun (varies)</t>
+          <t>May peak · Apr–Jun (varies)</t>
         </is>
       </c>
       <c r="C9" s="17" t="n"/>
@@ -852,7 +852,7 @@
       </c>
       <c r="G9" s="10" t="inlineStr">
         <is>
-          <t>Orders far in advance → 06 Holiday &amp; Event Checklists · sheet "Celebration Cakes (Apr-Jun)"</t>
+          <t>Orders far in advance (First Communions are strongest in Hispanic, Italian, Polish and Filipino parishes) → 06 Holiday &amp; Event Checklists · sheet "Celebration Cakes (Apr-Jun)"</t>
         </is>
       </c>
     </row>
@@ -883,7 +883,7 @@
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>Adapt the case to cold items: in hot weather, everything cream-filled goes in the refrigerated case at 41 °F or below</t>
+          <t>Adapt the case to summer items; all year round, everything cream-filled goes in the refrigerated case at 41 °F or below</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="G15" s="10" t="inlineStr">
         <is>
-          <t>Wholesale orders from other food businesses</t>
+          <t>Wholesale orders from other food businesses (wholesale may need its own license — check with your health department)</t>
         </is>
       </c>
     </row>
